--- a/Day 5/Guerrilla AI - Day 5 - Demo Start.xlsx
+++ b/Day 5/Guerrilla AI - Day 5 - Demo Start.xlsx
@@ -552,7 +552,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Follow the numbered steps below live with George. Everything happens in this workbook. Nothing to install, nothing to license.</t>
+          <t xml:space="preserve">Watch live. Reply in chat with a word or letter when invited. Try the workbook afterward at your own pace.</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="6" ht="21" customHeight="1">
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Same request, two prompts, very different answers.</t>
+          <t xml:space="preserve">Easier for you to scan? A = paragraph; B = headings. Reply in chat or think of your choice.</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
     <row r="11" ht="21" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Markdown tables move data without connectors or licenses.</t>
+          <t xml:space="preserve">Which separator is in this table? PIPE / COMMA. Reply in chat or think of your choice.</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t># Move tables in and out of AI tools
+          <t xml:space="preserve"># Move tables in and out of AI tools
 1. Copy the RegionSummary table in Excel, paste to a chatbot
 2. It arrives as a table the model reads cleanly
 3. Ask for results 'as a Markdown table'
 4. Paste the reply into Excel, then Data &gt; Text to Columns
-5. Delimiter: | (pipe), then trim the empty edge columns</t>
+5. Split on | (pipe). Remove the separator row and empty edge columns. Check headers and numbers.</t>
         </is>
       </c>
     </row>
@@ -636,14 +636,14 @@
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>✓  Takeaway</t>
+          <t xml:space="preserve">One small next step</t>
         </is>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Speaking the machine's language is the cheapest AI upgrade there is.</t>
+          <t xml:space="preserve">Add TASK or FORMAT to your next AI prompt. Choose one, run it, and check what improved.</t>
         </is>
       </c>
     </row>
